--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -2656,8 +2656,17 @@
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Stadio Nicola Ceravolo
+ (Catanzaro)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>14 650</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24.08.2024 13:30</t>
+          <t>25.08.2024 13:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sacchi J. L.
+          <t>Sozza S.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Ennio Tardini
- (Parma)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>27 906</t>
+          <t>43 147</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24.08.2024 13:30</t>
+          <t>25.08.2024 13:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Doveri D.
+          <t>Rapuano A.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25 144</t>
+          <t>28 177</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24.08.2024 15:45</t>
+          <t>25.08.2024 15:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Di Marco D.
+          <t>Zufferli L.
  (Ita)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80 018</t>
+          <t>70 634</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,50 +730,50 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.08.2024 15:45</t>
+          <t>25.08.2024 15:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mariani M.
+          <t>Pairetto L.
  (Ita)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Brianteo
- (Monza)</t>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>17 102</t>
+          <t>54 726</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -796,6 +796,844 @@
         </is>
       </c>
       <c r="P5" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>26.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Di Bello M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>16 416</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>771</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>26.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Giua A.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>39 211</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>77</v>
+      </c>
+      <c r="L7" t="n">
+        <v>771</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>30.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>11 150</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>771</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>30.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>77</v>
+      </c>
+      <c r="L9" t="n">
+        <v>771</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>31.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>38 279</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>77</v>
+      </c>
+      <c r="L10" t="n">
+        <v>771</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>31.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>40 670</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>771</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>31.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>77</v>
+      </c>
+      <c r="L12" t="n">
+        <v>771</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>31.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>54 726</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>77</v>
+      </c>
+      <c r="L13" t="n">
+        <v>771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>01.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>43 147</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>77</v>
+      </c>
+      <c r="L14" t="n">
+        <v>771</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>01.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>77</v>
+      </c>
+      <c r="L15" t="n">
+        <v>771</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>01.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>41 507</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>77</v>
+      </c>
+      <c r="L16" t="n">
+        <v>771</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>01.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>25 144</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>77</v>
+      </c>
+      <c r="L17" t="n">
+        <v>771</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25.08.2024 13:30</t>
+          <t>26.08.2024 13:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sozza S.
+          <t>Di Bello M.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
+          <t>Unipol Domus
+ (Cagliari)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>43 147</t>
+          <t>16 416</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25.08.2024 13:30</t>
+          <t>26.08.2024 15:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rapuano A.
+          <t>Giua A.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Olimpico di Torino
- (Turin)</t>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28 177</t>
+          <t>39 211</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +656,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25.08.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Zufferli L.
- (Ita)</t>
-        </is>
-      </c>
+          <t>30.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70 634</t>
+          <t>11 150</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,50 +725,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.08.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Pairetto L.
- (Ita)</t>
-        </is>
-      </c>
+          <t>30.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>54 726</t>
+          <t>80 018</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -804,50 +794,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>26.08.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Di Bello M.
- (Ita)</t>
-        </is>
-      </c>
+          <t>31.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Unipol Domus
- (Cagliari)</t>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16 416</t>
+          <t>38 279</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -878,50 +863,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26.08.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Giua A.
- (Ita)</t>
-        </is>
-      </c>
+          <t>31.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Marc'Antonio Bentegodi
- (Verona)</t>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>39 211</t>
+          <t>40 670</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -952,45 +932,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30.08.2024 13:30</t>
+          <t>31.08.2024 15:45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Pierluigi Penzo
- (Venice)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11 150</t>
+          <t>70 634</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1021,45 +1001,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>30.08.2024 15:45</t>
+          <t>31.08.2024 15:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80 018</t>
+          <t>54 726</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1090,45 +1070,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>31.08.2024 13:30</t>
+          <t>01.09.2024 13:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>38 279</t>
+          <t>43 147</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1159,45 +1139,45 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>31.08.2024 13:30</t>
+          <t>01.09.2024 13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stadio Via del Mare
- (Lecce)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>40 670</t>
+          <t>36 599</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1228,45 +1208,45 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>31.08.2024 15:45</t>
+          <t>01.09.2024 15:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>70 634</t>
+          <t>41 507</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1297,45 +1277,45 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>31.08.2024 15:45</t>
+          <t>01.09.2024 15:45</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>54 726</t>
+          <t>25 144</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1358,282 +1338,6 @@
         </is>
       </c>
       <c r="P13" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>01.09.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>43 147</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Monza</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>77</v>
-      </c>
-      <c r="L14" t="n">
-        <v>771</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>01.09.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>36 599</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Genoa</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>77</v>
-      </c>
-      <c r="L15" t="n">
-        <v>771</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>01.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Allianz Stadium
- (Turin)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>41 507</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>77</v>
-      </c>
-      <c r="L16" t="n">
-        <v>771</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>01.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>25 144</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>77</v>
-      </c>
-      <c r="L17" t="n">
-        <v>771</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26.08.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Di Bello M.
- (Ita)</t>
-        </is>
-      </c>
+          <t>30.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Unipol Domus
- (Cagliari)</t>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16 416</t>
+          <t>11 150</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +577,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26.08.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Giua A.
- (Ita)</t>
-        </is>
-      </c>
+          <t>30.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Marc'Antonio Bentegodi
- (Verona)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>39 211</t>
+          <t>80 018</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,45 +646,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.08.2024 13:30</t>
+          <t>31.08.2024 13:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Pierluigi Penzo
- (Venice)</t>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11 150</t>
+          <t>38 279</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -725,45 +715,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.08.2024 15:45</t>
+          <t>31.08.2024 13:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>80 018</t>
+          <t>40 670</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -794,45 +784,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>31.08.2024 13:30</t>
+          <t>31.08.2024 15:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>38 279</t>
+          <t>70 634</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -863,45 +853,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31.08.2024 13:30</t>
+          <t>31.08.2024 15:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Via del Mare
- (Lecce)</t>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>40 670</t>
+          <t>54 726</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -932,45 +922,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>31.08.2024 15:45</t>
+          <t>01.09.2024 13:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>70 634</t>
+          <t>43 147</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1001,45 +991,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31.08.2024 15:45</t>
+          <t>01.09.2024 13:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>54 726</t>
+          <t>36 599</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1070,45 +1060,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01.09.2024 13:30</t>
+          <t>01.09.2024 15:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>43 147</t>
+          <t>41 507</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1139,45 +1129,45 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01.09.2024 13:30</t>
+          <t>01.09.2024 15:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>36 599</t>
+          <t>25 144</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1200,144 +1190,6 @@
         </is>
       </c>
       <c r="P11" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>01.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Allianz Stadium
- (Turin)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>41 507</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>77</v>
-      </c>
-      <c r="L12" t="n">
-        <v>771</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>01.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>25 144</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>77</v>
-      </c>
-      <c r="L13" t="n">
-        <v>771</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,45 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30.08.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>31.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Marinelli L.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Pierluigi Penzo
- (Venice)</t>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11 150</t>
+          <t>38 279</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -577,45 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>30.08.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>31.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fabbri M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>80 018</t>
+          <t>40 670</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -646,45 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.08.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>31.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Massa D.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>38 279</t>
+          <t>70 634</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -715,45 +730,50 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.08.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>31.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tremolada P.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Via del Mare
- (Lecce)</t>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>40 670</t>
+          <t>54 726</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,45 +804,50 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>31.08.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>01.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>70 634</t>
+          <t>43 147</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -853,45 +878,50 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31.08.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>01.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ayroldi G.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>54 726</t>
+          <t>36 599</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -922,45 +952,50 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>01.09.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>01.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Guida M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>43 147</t>
+          <t>41 507</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -991,45 +1026,50 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01.09.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>01.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Prontera A.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>36 599</t>
+          <t>25 144</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1052,144 +1092,6 @@
         </is>
       </c>
       <c r="P9" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>01.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Allianz Stadium
- (Turin)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>41 507</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>77</v>
-      </c>
-      <c r="L10" t="n">
-        <v>771</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>01.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>25 144</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>77</v>
-      </c>
-      <c r="L11" t="n">
-        <v>771</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31.08.2024 13:30</t>
+          <t>01.09.2024 13:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Marinelli L.
+          <t>Colombo A.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>38 279</t>
+          <t>43 147</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31.08.2024 13:30</t>
+          <t>01.09.2024 13:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fabbri M.
+          <t>Ayroldi G.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Via del Mare
- (Lecce)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40 670</t>
+          <t>36 599</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.08.2024 15:45</t>
+          <t>01.09.2024 15:45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Massa D.
+          <t>Guida M.
  (Ita)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70 634</t>
+          <t>41 507</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,50 +730,50 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.08.2024 15:45</t>
+          <t>01.09.2024 15:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tremolada P.
+          <t>Prontera A.
  (Ita)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>54 726</t>
+          <t>25 144</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -796,302 +796,6 @@
         </is>
       </c>
       <c r="P5" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>01.09.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Colombo A.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>43 147</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Monza</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>77</v>
-      </c>
-      <c r="L6" t="n">
-        <v>771</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>01.09.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ayroldi G.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>36 599</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Genoa</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>77</v>
-      </c>
-      <c r="L7" t="n">
-        <v>771</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>01.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Guida M.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Allianz Stadium
- (Turin)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>41 507</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>77</v>
-      </c>
-      <c r="L8" t="n">
-        <v>771</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>01.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Prontera A.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>25 144</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>77</v>
-      </c>
-      <c r="L9" t="n">
-        <v>771</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>n7VN5MCd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01.09.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Colombo A.
- (Ita)</t>
-        </is>
-      </c>
+          <t>14.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>43 147</t>
+          <t>13 602</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +577,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>v1I9TP43</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01.09.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ayroldi G.
- (Ita)</t>
-        </is>
-      </c>
+          <t>14.09.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>36 599</t>
+          <t>16 284</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +646,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hCGaFZqg</t>
+          <t>SQjcKLRk</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>01.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Guida M.
- (Ita)</t>
-        </is>
-      </c>
+          <t>14.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Allianz Stadium
- (Turin)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>41 507</t>
+          <t>80 018</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,50 +715,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ZvTGnLc</t>
+          <t>zTBIR3ZF</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>01.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Prontera A.
- (Ita)</t>
-        </is>
-      </c>
+          <t>15.09.2024 07:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>25 144</t>
+          <t>36 599</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -796,6 +776,420 @@
         </is>
       </c>
       <c r="P5" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>15.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>21 747</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>771</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>15.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>28 177</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>77</v>
+      </c>
+      <c r="L7" t="n">
+        <v>771</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15.09.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>16 416</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>771</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>15.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>17 102</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>77</v>
+      </c>
+      <c r="L9" t="n">
+        <v>771</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>16.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>27 906</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>77</v>
+      </c>
+      <c r="L10" t="n">
+        <v>771</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>16.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>771</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1195,6 +1195,696 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>16 416</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>77</v>
+      </c>
+      <c r="L12" t="n">
+        <v>771</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>39 211</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>77</v>
+      </c>
+      <c r="L13" t="n">
+        <v>771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>21.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>11 150</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>77</v>
+      </c>
+      <c r="L14" t="n">
+        <v>771</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>21.09.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>41 507</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>77</v>
+      </c>
+      <c r="L15" t="n">
+        <v>771</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>21.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>40 670</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>77</v>
+      </c>
+      <c r="L16" t="n">
+        <v>771</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>22.09.2024 07:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>43 147</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>77</v>
+      </c>
+      <c r="L17" t="n">
+        <v>771</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>17 102</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>77</v>
+      </c>
+      <c r="L18" t="n">
+        <v>771</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>22.09.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>77</v>
+      </c>
+      <c r="L19" t="n">
+        <v>771</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>22.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>77</v>
+      </c>
+      <c r="L20" t="n">
+        <v>771</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>23.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>21 747</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>77</v>
+      </c>
+      <c r="L21" t="n">
+        <v>771</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,516 +508,1378 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>2ucWYubt</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.09.2024 07:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Giua A.
- (Ita)</t>
-        </is>
-      </c>
+          <t>20.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>16 416</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>77</v>
+      </c>
+      <c r="L2" t="n">
+        <v>771</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>20.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>39 211</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>77</v>
+      </c>
+      <c r="L3" t="n">
+        <v>771</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>21.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>11 150</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>77</v>
+      </c>
+      <c r="L4" t="n">
+        <v>771</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>21.09.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>41 507</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>77</v>
+      </c>
+      <c r="L5" t="n">
+        <v>771</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>21.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>40 670</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>771</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>22.09.2024 07:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>43 147</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>77</v>
+      </c>
+      <c r="L7" t="n">
+        <v>771</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>22.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>17 102</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>771</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>22.09.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>77</v>
+      </c>
+      <c r="L9" t="n">
+        <v>771</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>77</v>
+      </c>
+      <c r="L10" t="n">
+        <v>771</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>23.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>24 950</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>771</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>27.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>77</v>
+      </c>
+      <c r="L12" t="n">
+        <v>771</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>25 144</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>77</v>
+      </c>
+      <c r="L13" t="n">
+        <v>771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>28.09.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Stadio Luigi Ferraris
  (Genoa)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>36 599</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>d0PJxeie</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Genoa</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>77</v>
-      </c>
-      <c r="L2" t="n">
-        <v>771</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>zFWqD4KM</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>15.09.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Sacchi J. L.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Gewiss Stadium
- (Bergamo)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>21 747</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>77</v>
+      </c>
+      <c r="L14" t="n">
+        <v>771</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>28.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>38 279</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>8C9JjMXu</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Atalanta</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>77</v>
-      </c>
-      <c r="L3" t="n">
-        <v>771</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>4WHcOkpL</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>15.09.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Colombo A.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="K15" t="n">
+        <v>77</v>
+      </c>
+      <c r="L15" t="n">
+        <v>771</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>29.09.2024 07:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Stadio Olimpico di Torino
  (Turin)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>28 177</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>MZFZnvX4</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Torino</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>77</v>
-      </c>
-      <c r="L4" t="n">
-        <v>771</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>6cNF7rrp</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>15.09.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>La Penna F.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Unipol Domus
- (Cagliari)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>16 416</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>77</v>
+      </c>
+      <c r="L16" t="n">
+        <v>771</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>77</v>
+      </c>
+      <c r="L17" t="n">
+        <v>771</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>13 602</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>77</v>
+      </c>
+      <c r="L18" t="n">
+        <v>771</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>29.09.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>16 284</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>77</v>
+      </c>
+      <c r="L19" t="n">
+        <v>771</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>29.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>54 726</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>69Dxbc61</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Napoli</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>77</v>
-      </c>
-      <c r="L5" t="n">
-        <v>771</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Esk5Iad2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>15.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Pairetto L.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Brianteo
- (Monza)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>17 102</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>4YSMlwj7</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Monza</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Inter</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>77</v>
-      </c>
-      <c r="L6" t="n">
-        <v>771</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>WIJkQBF8</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>16.09.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Abisso R.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="K20" t="n">
+        <v>77</v>
+      </c>
+      <c r="L20" t="n">
+        <v>771</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>30.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Stadio Ennio Tardini
  (Parma)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>27 906</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>6DxlaxHN</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Parma</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>77</v>
-      </c>
-      <c r="L7" t="n">
-        <v>771</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>rgFQPs4S</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>16.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Zufferli L.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stadio Olimpico
- (Rome)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>70 634</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>77</v>
-      </c>
-      <c r="L8" t="n">
-        <v>771</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>77</v>
+      </c>
+      <c r="L21" t="n">
+        <v>771</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,516 +508,1452 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.09.2024 07:30</t>
+          <t>23.09.2024 15:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Giua A.
+          <t>Tremolada P.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>24 950</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>77</v>
+      </c>
+      <c r="L2" t="n">
+        <v>771</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>27.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>77</v>
+      </c>
+      <c r="L3" t="n">
+        <v>771</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>25 144</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>77</v>
+      </c>
+      <c r="L4" t="n">
+        <v>771</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>28.09.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
         <is>
           <t>Stadio Luigi Ferraris
  (Genoa)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>36 599</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
         <is>
           <t>d0PJxeie</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Genoa</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>77</v>
+      </c>
+      <c r="L5" t="n">
+        <v>771</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>28.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>38 279</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>771</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>29.09.2024 07:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>28 177</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>77</v>
+      </c>
+      <c r="L7" t="n">
+        <v>771</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>zVqqL0ma</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>AS Roma</t>
         </is>
       </c>
-      <c r="K2" t="n">
-        <v>77</v>
-      </c>
-      <c r="L2" t="n">
-        <v>771</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>zFWqD4KM</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>15.09.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Sacchi J. L.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>771</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>13 602</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>77</v>
+      </c>
+      <c r="L9" t="n">
+        <v>771</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>29.09.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>16 284</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>77</v>
+      </c>
+      <c r="L10" t="n">
+        <v>771</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>29.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>54 726</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>771</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>30.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>27 906</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>77</v>
+      </c>
+      <c r="L12" t="n">
+        <v>771</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>z3jsi9f5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>04.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>54 726</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>77</v>
+      </c>
+      <c r="L13" t="n">
+        <v>771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8SWavWAa</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>04.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>39 211</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>77</v>
+      </c>
+      <c r="L14" t="n">
+        <v>771</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WUqjkmPH</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>05.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>25 144</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>77</v>
+      </c>
+      <c r="L15" t="n">
+        <v>771</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EB8yv2aJ</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>05.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Gewiss Stadium
  (Bergamo)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>21 747</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>24 950</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>8C9JjMXu</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Atalanta</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>77</v>
-      </c>
-      <c r="L3" t="n">
-        <v>771</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>4WHcOkpL</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>15.09.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Colombo A.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Stadio Olimpico di Torino
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>77</v>
+      </c>
+      <c r="L16" t="n">
+        <v>771</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ttV7xAuC</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>05.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>77</v>
+      </c>
+      <c r="L17" t="n">
+        <v>771</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>06.10.2024 07:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
  (Turin)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>28 177</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MZFZnvX4</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>77</v>
-      </c>
-      <c r="L4" t="n">
-        <v>771</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>6cNF7rrp</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>15.09.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>La Penna F.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Unipol Domus
- (Cagliari)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>16 416</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>41 507</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>SCGVmKHb</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Cagliari</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>77</v>
-      </c>
-      <c r="L5" t="n">
-        <v>771</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Esk5Iad2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>15.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Pairetto L.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="K18" t="n">
+        <v>77</v>
+      </c>
+      <c r="L18" t="n">
+        <v>771</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>38 279</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>77</v>
+      </c>
+      <c r="L19" t="n">
+        <v>771</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>77</v>
+      </c>
+      <c r="L20" t="n">
+        <v>771</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>06.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Brianteo
  (Monza)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>17 102</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>4YSMlwj7</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Monza</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Inter</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>77</v>
-      </c>
-      <c r="L6" t="n">
-        <v>771</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>WIJkQBF8</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>16.09.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Abisso R.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Stadio Ennio Tardini
- (Parma)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>27 906</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>77</v>
-      </c>
-      <c r="L7" t="n">
-        <v>771</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>rgFQPs4S</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>16.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Zufferli L.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stadio Olimpico
- (Rome)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>70 634</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>77</v>
-      </c>
-      <c r="L8" t="n">
-        <v>771</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>77</v>
+      </c>
+      <c r="L21" t="n">
+        <v>771</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>06.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>43 147</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>77</v>
+      </c>
+      <c r="L22" t="n">
+        <v>771</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OAeKROjD</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23.09.2024 15:45</t>
+          <t>27.09.2024 15:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tremolada P.
+          <t>Zufferli L.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Gewiss Stadium
- (Bergamo)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24 950</t>
+          <t>80 018</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,45 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>pIgDNCf3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>28.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sacchi J. L.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>80 018</t>
+          <t>25 144</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -651,45 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>KIQjmWIj</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28.09.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>28.09.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25 144</t>
+          <t>36 599</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -720,45 +730,50 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.09.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>28.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Rapuano A.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36 599</t>
+          <t>38 279</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -789,45 +804,50 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>28.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>29.09.2024 07:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sozza S.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>38 279</t>
+          <t>28 177</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -858,45 +878,50 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29.09.2024 07:30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>29.09.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Abisso R.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Olimpico di Torino
- (Turin)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28 177</t>
+          <t>70 634</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -927,7 +952,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -935,37 +960,42 @@
           <t>29.09.2024 10:00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Giua A.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>70 634</t>
+          <t>13 602</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -996,45 +1026,50 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>29.09.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>29.09.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Aureliano G.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Sinigaglia
- (Como)</t>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13 602</t>
+          <t>16 284</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1065,45 +1100,50 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>29.09.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>29.09.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Manganiello G.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stadio Carlo Castellani
- (Empoli)</t>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16 284</t>
+          <t>54 726</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1126,834 +1166,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>29.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>54 726</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Monza</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>77</v>
-      </c>
-      <c r="L11" t="n">
-        <v>771</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vuXo7iAM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>30.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Stadio Ennio Tardini
- (Parma)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>27 906</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>77</v>
-      </c>
-      <c r="L12" t="n">
-        <v>771</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>z3jsi9f5</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>04.10.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>54 726</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>77</v>
-      </c>
-      <c r="L13" t="n">
-        <v>771</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8SWavWAa</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>04.10.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stadio Marc'Antonio Bentegodi
- (Verona)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>39 211</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>MkPmVv50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Venezia</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>77</v>
-      </c>
-      <c r="L14" t="n">
-        <v>771</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WUqjkmPH</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>05.10.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>25 144</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>rXw8YKDE</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Udinese</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>77</v>
-      </c>
-      <c r="L15" t="n">
-        <v>771</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>EB8yv2aJ</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>05.10.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Gewiss Stadium
- (Bergamo)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>24 950</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>8C9JjMXu</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Atalanta</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>d0PJxeie</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Genoa</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>77</v>
-      </c>
-      <c r="L16" t="n">
-        <v>771</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ttV7xAuC</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>05.10.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>80 018</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Inter</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>MZFZnvX4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>77</v>
-      </c>
-      <c r="L17" t="n">
-        <v>771</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>x8OGzlAO</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>06.10.2024 07:30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Allianz Stadium
- (Turin)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>41 507</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>C06aJvIB</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Juventus</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>77</v>
-      </c>
-      <c r="L18" t="n">
-        <v>771</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dzYLoEIP</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>06.10.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>38 279</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0M9xNN8N</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Bologna</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Parma</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>77</v>
-      </c>
-      <c r="L19" t="n">
-        <v>771</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>SW3Qfiet</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>06.10.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Stadio Olimpico
- (Rome)</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>70 634</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>URcSl02h</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Lazio</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Empoli</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>77</v>
-      </c>
-      <c r="L20" t="n">
-        <v>771</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>lnhZhVPh</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>06.10.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Brianteo
- (Monza)</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>17 102</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Monza</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>zVqqL0ma</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>AS Roma</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>77</v>
-      </c>
-      <c r="L21" t="n">
-        <v>771</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>SIOithtm</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>06.10.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>43 147</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8Sa8HInO</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>AC Milan</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>77</v>
-      </c>
-      <c r="L22" t="n">
-        <v>771</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27.09.2024 15:45</t>
+          <t>29.09.2024 07:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Zufferli L.
+          <t>Sozza S.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80 018</t>
+          <t>28 177</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>28.09.2024 10:00</t>
+          <t>29.09.2024 10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sacchi J. L.
+          <t>Abisso R.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25 144</t>
+          <t>70 634</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>28.09.2024 13:00</t>
+          <t>29.09.2024 10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Colombo A.
+          <t>Giua A.
  (Ita)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>36 599</t>
+          <t>13 602</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,50 +730,50 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.09.2024 15:45</t>
+          <t>29.09.2024 13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rapuano A.
+          <t>Aureliano G.
  (Ita)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38 279</t>
+          <t>16 284</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -804,50 +804,50 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29.09.2024 07:30</t>
+          <t>29.09.2024 15:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sozza S.
+          <t>Manganiello G.
  (Ita)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Olimpico di Torino
- (Turin)</t>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28 177</t>
+          <t>54 726</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -878,50 +878,50 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>vuXo7iAM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>29.09.2024 10:00</t>
+          <t>30.09.2024 15:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Abisso R.
+          <t>Fourneau F.
  (Ita)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>70 634</t>
+          <t>27 906</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -944,228 +944,6 @@
         </is>
       </c>
       <c r="P7" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>29.09.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Giua A.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Stadio Giuseppe Sinigaglia
- (Como)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>13 602</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ttyLthOA</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Como</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>rJVAIaHo</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Verona</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>77</v>
-      </c>
-      <c r="L8" t="n">
-        <v>771</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>29.09.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Aureliano G.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Stadio Carlo Castellani
- (Empoli)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>16 284</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0ESCnI1H</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Empoli</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>77</v>
-      </c>
-      <c r="L9" t="n">
-        <v>771</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>29.09.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Manganiello G.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>54 726</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Monza</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>77</v>
-      </c>
-      <c r="L10" t="n">
-        <v>771</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>z3jsi9f5</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29.09.2024 07:30</t>
+          <t>04.10.2024 13:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Sozza S.
+          <t>Feliciani E.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Olimpico di Torino
- (Turin)</t>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28 177</t>
+          <t>54 726</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,40 +582,40 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>8SWavWAa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>29.09.2024 10:00</t>
+          <t>04.10.2024 15:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Abisso R.
+          <t>Guida M.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>70 634</t>
+          <t>39 211</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -656,50 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>WUqjkmPH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>29.09.2024 10:00</t>
+          <t>05.10.2024 10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Giua A.
+          <t>Mariani M.
  (Ita)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Sinigaglia
- (Como)</t>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13 602</t>
+          <t>25 144</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,50 +730,50 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>EB8yv2aJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.09.2024 13:00</t>
+          <t>05.10.2024 13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aureliano G.
+          <t>Chiffi D.
  (Ita)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Carlo Castellani
- (Empoli)</t>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16 284</t>
+          <t>24 950</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -804,50 +804,50 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WETw9DuA</t>
+          <t>ttV7xAuC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29.09.2024 15:45</t>
+          <t>05.10.2024 15:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Manganiello G.
+          <t>Marcenaro M.
  (Ita)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54 726</t>
+          <t>80 018</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -878,40 +878,40 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vuXo7iAM</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30.09.2024 15:45</t>
+          <t>06.10.2024 07:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fourneau F.
+          <t>Marinelli L.
  (Ita)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Ennio Tardini
- (Parma)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27 906</t>
+          <t>41 507</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -944,6 +944,440 @@
         </is>
       </c>
       <c r="P7" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Di Bello M.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>38 279</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>771</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ayroldi G.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>77</v>
+      </c>
+      <c r="L9" t="n">
+        <v>771</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>06.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>La Penna F.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>17 102</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>77</v>
+      </c>
+      <c r="L10" t="n">
+        <v>771</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>06.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pairetto L.
+ (Ita)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>43 147</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>771</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>13 602</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>77</v>
+      </c>
+      <c r="L12" t="n">
+        <v>771</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>77</v>
+      </c>
+      <c r="L13" t="n">
+        <v>771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z3jsi9f5</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04.10.2024 13:30</t>
+          <t>06.10.2024 07:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Feliciani E.
+          <t>Marinelli L.
  (Ita)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>54 726</t>
+          <t>41 507</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>04.10.2024 15:45</t>
+          <t>06.10.2024 10:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Guida M.
+          <t>Di Bello M.
  (Ita)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Marc'Antonio Bentegodi
- (Verona)</t>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>39 211</t>
+          <t>38 279</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
+          <t>SW3Qfiet</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05.10.2024 10:00</t>
+          <t>06.10.2024 10:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mariani M.
+          <t>Ayroldi G.
  (Ita)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25 144</t>
+          <t>70 634</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,50 +730,50 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05.10.2024 13:00</t>
+          <t>06.10.2024 13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chiffi D.
+          <t>La Penna F.
  (Ita)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gewiss Stadium
- (Bergamo)</t>
+          <t>Brianteo
+ (Monza)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>24 950</t>
+          <t>17 102</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -804,50 +804,50 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05.10.2024 15:45</t>
+          <t>06.10.2024 15:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Marcenaro M.
+          <t>Pairetto L.
  (Ita)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>80 018</t>
+          <t>43 147</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -878,50 +878,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06.10.2024 07:30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Marinelli L.
- (Ita)</t>
-        </is>
-      </c>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Allianz Stadium
- (Turin)</t>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>41 507</t>
+          <t>13 602</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -952,50 +947,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06.10.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Di Bello M.
- (Ita)</t>
-        </is>
-      </c>
+          <t>19.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>38 279</t>
+          <t>36 599</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0M9xNN8N</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Bologna</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>6DxlaxHN</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Parma</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1026,50 +1016,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06.10.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ayroldi G.
- (Ita)</t>
-        </is>
-      </c>
+          <t>19.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>70 634</t>
+          <t>80 018</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1100,50 +1085,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>06.10.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>La Penna F.
- (Ita)</t>
-        </is>
-      </c>
+          <t>19.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Brianteo
- (Monza)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17 102</t>
+          <t>41 507</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1174,50 +1154,45 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>06.10.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Pairetto L.
- (Ita)</t>
-        </is>
-      </c>
+          <t>20.10.2024 07:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>43 147</t>
+          <t>16 284</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1248,45 +1223,45 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19.10.2024 10:00</t>
+          <t>20.10.2024 10:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Sinigaglia
- (Como)</t>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>13 602</t>
+          <t>40 670</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1317,45 +1292,45 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19.10.2024 10:00</t>
+          <t>20.10.2024 10:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>36 599</t>
+          <t>11 150</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1378,6 +1353,144 @@
         </is>
       </c>
       <c r="P13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GMBD7YY8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>20.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>16 416</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>77</v>
+      </c>
+      <c r="L14" t="n">
+        <v>771</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0lpzB7u1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>77</v>
+      </c>
+      <c r="L15" t="n">
+        <v>771</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,7 +516,12 @@
           <t>19.10.2024 10:00</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Fabbri M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Stadio Giuseppe Sinigaglia
@@ -585,7 +590,12 @@
           <t>19.10.2024 10:00</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Doveri D.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Stadio Luigi Ferraris
@@ -654,7 +664,12 @@
           <t>19.10.2024 13:00</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Chiffi D.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Stadio Giuseppe Meazza (San Siro)
@@ -723,7 +738,12 @@
           <t>19.10.2024 15:45</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sacchi J. L.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Allianz Stadium
@@ -792,7 +812,12 @@
           <t>20.10.2024 07:30</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Abisso R.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Stadio Carlo Castellani
@@ -861,7 +886,12 @@
           <t>20.10.2024 10:00</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fourneau F.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Stadio Via del Mare
@@ -930,7 +960,12 @@
           <t>20.10.2024 10:00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Zufferli L.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Stadio Pierluigi Penzo
@@ -999,7 +1034,12 @@
           <t>20.10.2024 13:00</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Aureliano G.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Unipol Domus
@@ -1068,7 +1108,12 @@
           <t>20.10.2024 15:45</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Massa D.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Stadio Olimpico
@@ -1137,7 +1182,12 @@
           <t>21.10.2024 15:45</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Dionisi F.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Stadio Marc'Antonio Bentegodi
@@ -2087,6 +2137,351 @@
         </is>
       </c>
       <c r="P24" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>30.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>16 284</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>77</v>
+      </c>
+      <c r="L25" t="n">
+        <v>771</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>30.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>11 150</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>77</v>
+      </c>
+      <c r="L26" t="n">
+        <v>771</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>24 950</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>77</v>
+      </c>
+      <c r="L27" t="n">
+        <v>771</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>41 507</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>77</v>
+      </c>
+      <c r="L28" t="n">
+        <v>771</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>31.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>77</v>
+      </c>
+      <c r="L29" t="n">
+        <v>771</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2487,6 +2487,144 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>31.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>77</v>
+      </c>
+      <c r="L30" t="n">
+        <v>771</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>31.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>13 602</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>77</v>
+      </c>
+      <c r="L31" t="n">
+        <v>771</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,442 +508,2068 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20.10.2024 07:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Abisso R.
- (Ita)</t>
-        </is>
-      </c>
+          <t>25.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>25 144</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>77</v>
+      </c>
+      <c r="L2" t="n">
+        <v>771</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>bLD0NyVN</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>25.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>28 177</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>77</v>
+      </c>
+      <c r="L3" t="n">
+        <v>771</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>UuMqRJVb</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26.10.2024 10:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>54 726</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>77</v>
+      </c>
+      <c r="L4" t="n">
+        <v>771</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>8f71RSPs</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26.10.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>38 279</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>77</v>
+      </c>
+      <c r="L5" t="n">
+        <v>771</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>OMVUWl2K</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>26.10.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>24 950</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>77</v>
+      </c>
+      <c r="L6" t="n">
+        <v>771</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>jeAhPc0B</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>27.10.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>27 906</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>77</v>
+      </c>
+      <c r="L7" t="n">
+        <v>771</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>27.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>77</v>
+      </c>
+      <c r="L8" t="n">
+        <v>771</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>27.10.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>17 102</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>77</v>
+      </c>
+      <c r="L9" t="n">
+        <v>771</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>27.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>77</v>
+      </c>
+      <c r="L10" t="n">
+        <v>771</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>27.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>43 147</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>771</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>29.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Unipol Domus
+ (Cagliari)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>16 416</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>77</v>
+      </c>
+      <c r="L12" t="n">
+        <v>771</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>29.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>40 670</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>77</v>
+      </c>
+      <c r="L13" t="n">
+        <v>771</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>29.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>77</v>
+      </c>
+      <c r="L14" t="n">
+        <v>771</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>30.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Stadio Carlo Castellani
  (Empoli)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>16 284</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>0ESCnI1H</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Empoli</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>77</v>
-      </c>
-      <c r="L2" t="n">
-        <v>771</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>AJ5eIkmR</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>20.10.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Fourneau F.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Stadio Via del Mare
- (Lecce)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>40 670</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>G8lYsMgU</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Lecce</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>77</v>
-      </c>
-      <c r="L3" t="n">
-        <v>771</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>dGwq9oAD</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>20.10.2024 10:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Zufferli L.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>77</v>
+      </c>
+      <c r="L15" t="n">
+        <v>771</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>30.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Stadio Pierluigi Penzo
  (Venice)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>11 150</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>MkPmVv50</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Venezia</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>77</v>
+      </c>
+      <c r="L16" t="n">
+        <v>771</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>24 950</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>8C9JjMXu</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Atalanta</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>77</v>
-      </c>
-      <c r="L4" t="n">
-        <v>771</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>GMBD7YY8</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>20.10.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Aureliano G.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Unipol Domus
- (Cagliari)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>16 416</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>SCGVmKHb</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Cagliari</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>MZFZnvX4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Torino</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>77</v>
-      </c>
-      <c r="L5" t="n">
-        <v>771</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>0lpzB7u1</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>20.10.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Massa D.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>77</v>
+      </c>
+      <c r="L17" t="n">
+        <v>771</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>30.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Allianz Stadium
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>41 507</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>77</v>
+      </c>
+      <c r="L18" t="n">
+        <v>771</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>31.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>36 599</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>77</v>
+      </c>
+      <c r="L19" t="n">
+        <v>771</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>31.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Stadio Olimpico
  (Rome)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>70 634</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>zVqqL0ma</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>AS Roma</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Inter</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>77</v>
-      </c>
-      <c r="L6" t="n">
-        <v>771</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>McP0d8Q7</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>21.10.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Dionisi F.
- (Ita)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>77</v>
+      </c>
+      <c r="L20" t="n">
+        <v>771</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>31.10.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Sinigaglia
+ (Como)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>13 602</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>77</v>
+      </c>
+      <c r="L21" t="n">
+        <v>771</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Stadio Renato Dall'Ara
+ (Bologna)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>38 279</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0M9xNN8N</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>G8lYsMgU</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Lecce</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>77</v>
+      </c>
+      <c r="L22" t="n">
+        <v>771</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>02.11.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bluenergy Stadium - Stadio Friuli
+ (Udine)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>25 144</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>rXw8YKDE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>77</v>
+      </c>
+      <c r="L23" t="n">
+        <v>771</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>02.11.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Brianteo
+ (Monza)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>17 102</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>4YSMlwj7</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Monza</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>77</v>
+      </c>
+      <c r="L24" t="n">
+        <v>771</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>03.11.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Stadio Diego Armando Maradona
+ (Naples)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>54 726</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>69Dxbc61</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>8C9JjMXu</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>77</v>
+      </c>
+      <c r="L25" t="n">
+        <v>771</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>03.11.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico di Torino
+ (Turin)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>28 177</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>MZFZnvX4</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Torino</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Q3A3IbXH</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>77</v>
+      </c>
+      <c r="L26" t="n">
+        <v>771</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>03.11.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Stadio Marc'Antonio Bentegodi
  (Verona)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>39 211</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>rJVAIaHo</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Verona</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4YSMlwj7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Monza</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>77</v>
-      </c>
-      <c r="L7" t="n">
-        <v>771</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>zVqqL0ma</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>77</v>
+      </c>
+      <c r="L27" t="n">
+        <v>771</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>03.11.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>80 018</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>MkPmVv50</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Venezia</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>77</v>
+      </c>
+      <c r="L28" t="n">
+        <v>771</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>04.11.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Stadio Carlo Castellani
+ (Empoli)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>16 284</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0ESCnI1H</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Empoli</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ttyLthOA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>77</v>
+      </c>
+      <c r="L29" t="n">
+        <v>771</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>04.11.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Stadio Ennio Tardini
+ (Parma)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>27 906</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>6DxlaxHN</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Parma</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>d0PJxeie</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>77</v>
+      </c>
+      <c r="L30" t="n">
+        <v>771</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>04.11.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Stadio Olimpico
+ (Rome)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>70 634</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>URcSl02h</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>SCGVmKHb</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Cagliari</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>77</v>
+      </c>
+      <c r="L31" t="n">
+        <v>771</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -508,45 +508,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rJ8JNC5k</t>
+          <t>bR8Aj2ug</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>02.11.2024 11:00</t>
+          <t>07.11.2024 16:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Renato Dall'Ara
- (Bologna)</t>
+          <t>Stadio Luigi Ferraris
+ (Genoa)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>38 279</t>
+          <t>36 599</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>d0PJxeie</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>ttyLthOA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -577,45 +577,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pOryx3Qa</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>02.11.2024 14:00</t>
+          <t>08.11.2024 16:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bluenergy Stadium - Stadio Friuli
- (Udine)</t>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25 144</t>
+          <t>40 670</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -646,45 +646,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Gpn0zjke</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>02.11.2024 16:45</t>
+          <t>09.11.2024 11:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Brianteo
- (Monza)</t>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17 102</t>
+          <t>11 150</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -715,45 +715,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CCu9YTJ7</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>03.11.2024 08:30</t>
+          <t>09.11.2024 14:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadio Diego Armando Maradona
- (Naples)</t>
+          <t>Unipol Domus
+ (Cagliari)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>54 726</t>
+          <t>16 416</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>69Dxbc61</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,45 +784,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b7pTwPem</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>03.11.2024 11:00</t>
+          <t>09.11.2024 16:45</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Stadio Olimpico di Torino
+          <t>Allianz Stadium
  (Turin)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>28 177</t>
+          <t>41 507</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>MZFZnvX4</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Torino</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Q3A3IbXH</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Fiorentina</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -853,45 +853,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WvkEqfS8</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>03.11.2024 14:00</t>
+          <t>10.11.2024 08:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stadio Marc'Antonio Bentegodi
- (Verona)</t>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>39 211</t>
+          <t>24 950</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -922,45 +922,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v5hMsYdL</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>03.11.2024 16:45</t>
+          <t>10.11.2024 11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Giuseppe Meazza (San Siro)
- (Milan)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80 018</t>
+          <t>70 634</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Iw7eKK25</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Inter</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -991,45 +991,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jqCRLjz2</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>04.11.2024 14:30</t>
+          <t>10.11.2024 11:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Carlo Castellani
- (Empoli)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>16 284</t>
+          <t>43 147</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1060,45 +1060,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vJXfdXBE</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>04.11.2024 14:30</t>
+          <t>10.11.2024 14:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stadio Ennio Tardini
- (Parma)</t>
+          <t>Brianteo
+ (Monza)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>27 906</t>
+          <t>17 102</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1129,45 +1129,45 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rXmhxCKr</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>04.11.2024 16:45</t>
+          <t>10.11.2024 16:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>70 634</t>
+          <t>80 018</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="K11" t="n">

--- a/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/italy/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,45 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bR8Aj2ug</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07.11.2024 16:45</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>08.11.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Sacchi J. L.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadio Luigi Ferraris
- (Genoa)</t>
+          <t>Stadio Via del Mare
+ (Lecce)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>36 599</t>
+          <t>40 670</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>d0PJxeie</t>
+          <t>G8lYsMgU</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ttyLthOA</t>
+          <t>0ESCnI1H</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -577,45 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OYgzob9U</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08.11.2024 16:45</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>09.11.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Chiffi D.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stadio Via del Mare
- (Lecce)</t>
+          <t>Stadio Pierluigi Penzo
+ (Venice)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40 670</t>
+          <t>11 150</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>G8lYsMgU</t>
+          <t>MkPmVv50</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0ESCnI1H</t>
+          <t>6DxlaxHN</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -646,45 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hO2h1JgB</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09.11.2024 11:00</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>09.11.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fabbri M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadio Pierluigi Penzo
- (Venice)</t>
+          <t>Unipol Domus
+ (Cagliari)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11 150</t>
+          <t>16 416</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MkPmVv50</t>
+          <t>SCGVmKHb</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6DxlaxHN</t>
+          <t>8Sa8HInO</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -715,45 +730,50 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>E3zhYKPO</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09.11.2024 14:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>09.11.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sozza S.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Unipol Domus
- (Cagliari)</t>
+          <t>Allianz Stadium
+ (Turin)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>16 416</t>
+          <t>41 507</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SCGVmKHb</t>
+          <t>C06aJvIB</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8Sa8HInO</t>
+          <t>MZFZnvX4</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,45 +804,50 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>S60RnKvI</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09.11.2024 16:45</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>10.11.2024 08:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Di Bello M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Allianz Stadium
- (Turin)</t>
+          <t>Gewiss Stadium
+ (Bergamo)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>41 507</t>
+          <t>24 950</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>C06aJvIB</t>
+          <t>8C9JjMXu</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Atalanta</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MZFZnvX4</t>
+          <t>rXw8YKDE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -853,45 +878,50 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tjxpzseC</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10.11.2024 08:30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>10.11.2024 11:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Manganiello G.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Gewiss Stadium
- (Bergamo)</t>
+          <t>Stadio Olimpico
+ (Rome)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>24 950</t>
+          <t>70 634</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8C9JjMXu</t>
+          <t>zVqqL0ma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Atalanta</t>
+          <t>AS Roma</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>rXw8YKDE</t>
+          <t>0M9xNN8N</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -922,7 +952,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pbap3uPb</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -930,37 +960,42 @@
           <t>10.11.2024 11:00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Zufferli L.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stadio Olimpico
- (Rome)</t>
+          <t>Stadio Artemio Franchi
+ (Florence)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>70 634</t>
+          <t>43 147</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>zVqqL0ma</t>
+          <t>Q3A3IbXH</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>AS Roma</t>
+          <t>Fiorentina</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0M9xNN8N</t>
+          <t>rJVAIaHo</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Verona</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -991,45 +1026,50 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hU52hOAt</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10.11.2024 11:00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>10.11.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Colombo A.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stadio Artemio Franchi
- (Florence)</t>
+          <t>Brianteo
+ (Monza)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>43 147</t>
+          <t>17 102</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Q3A3IbXH</t>
+          <t>4YSMlwj7</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fiorentina</t>
+          <t>Monza</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>rJVAIaHo</t>
+          <t>URcSl02h</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Verona</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1060,45 +1100,50 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>voUq51fn</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10.11.2024 14:00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>10.11.2024 16:45</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mariani M.
+ (Ita)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Brianteo
- (Monza)</t>
+          <t>Stadio Giuseppe Meazza (San Siro)
+ (Milan)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>17 102</t>
+          <t>80 018</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4YSMlwj7</t>
+          <t>Iw7eKK25</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Monza</t>
+          <t>Inter</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>URcSl02h</t>
+          <t>69Dxbc61</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1129,67 +1174,136 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KtcJltA5</t>
+          <t>WENRFI84</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10.11.2024 16:45</t>
+          <t>23.11.2024 11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Stadio Marc'Antonio Bentegodi
+ (Verona)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>39 211</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>rJVAIaHo</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Verona</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Iw7eKK25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Inter</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>77</v>
+      </c>
+      <c r="L11" t="n">
+        <v>771</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Serie A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z7KrCz8T</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>23.11.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>Stadio Giuseppe Meazza (San Siro)
  (Milan)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>80 018</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Iw7eKK25</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Inter</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>69Dxbc61</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8Sa8HInO</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>C06aJvIB</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>77</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" t="n">
         <v>771</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>italy</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>
